--- a/exports/trend_1d/MUTHOOTFIN_full_report.xlsx
+++ b/exports/trend_1d/MUTHOOTFIN_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>14.46</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42081</v>
+        <v>42082</v>
       </c>
       <c r="H2" t="n">
-        <v>202.55</v>
+        <v>195.6</v>
       </c>
       <c r="I2" t="n">
         <v>202.1377123417948</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K2" t="n">
-        <v>1.86</v>
+        <v>-1.63</v>
       </c>
       <c r="L2" t="n">
         <v>4.17</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>14.31</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42184</v>
+        <v>42185</v>
       </c>
       <c r="H3" t="n">
-        <v>189</v>
+        <v>202.05</v>
       </c>
       <c r="I3" t="n">
         <v>195.8475500835806</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K3" t="n">
-        <v>3.37</v>
+        <v>-3.3</v>
       </c>
       <c r="L3" t="n">
         <v>9.25</v>
@@ -612,7 +647,7 @@
         <v>3.09</v>
       </c>
       <c r="N3" t="n">
-        <v>4.74</v>
+        <v>6.9</v>
       </c>
       <c r="O3" t="n">
         <v>-3.43</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>13.63</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42223</v>
+        <v>42226</v>
       </c>
       <c r="H4" t="n">
-        <v>187.45</v>
+        <v>183.35</v>
       </c>
       <c r="I4" t="n">
         <v>187.4221325142331</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.23</v>
+        <v>-9.26</v>
       </c>
       <c r="L4" t="n">
-        <v>8.119999999999999</v>
+        <v>10.42</v>
       </c>
       <c r="M4" t="n">
         <v>1.7</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>14.22</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42284</v>
+        <v>42285</v>
       </c>
       <c r="H5" t="n">
-        <v>173.9</v>
+        <v>180.4</v>
       </c>
       <c r="I5" t="n">
         <v>178.4617911097917</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K5" t="n">
-        <v>5.15</v>
+        <v>1.61</v>
       </c>
       <c r="L5" t="n">
         <v>4.06</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>14.8</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42366</v>
+        <v>42367</v>
       </c>
       <c r="H6" t="n">
-        <v>178.85</v>
+        <v>177.1</v>
       </c>
       <c r="I6" t="n">
         <v>177.1071904617355</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.86</v>
+        <v>-1.83</v>
       </c>
       <c r="L6" t="n">
         <v>5.18</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.17</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42380</v>
+        <v>42381</v>
       </c>
       <c r="H7" t="n">
-        <v>185.85</v>
+        <v>189.9</v>
       </c>
       <c r="I7" t="n">
         <v>189.4922225152445</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.94</v>
+        <v>-7.23</v>
       </c>
       <c r="L7" t="n">
         <v>8.550000000000001</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.82</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42426</v>
+        <v>42429</v>
       </c>
       <c r="H8" t="n">
-        <v>179.4</v>
+        <v>173.85</v>
       </c>
       <c r="I8" t="n">
         <v>174.4499943966804</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.53</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>11.61</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>12.9</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42473</v>
+        <v>42478</v>
       </c>
       <c r="H9" t="n">
-        <v>183.95</v>
+        <v>186.35</v>
       </c>
       <c r="I9" t="n">
         <v>185.2482104530308</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.81</v>
+        <v>-7.19</v>
       </c>
       <c r="L9" t="n">
-        <v>6.33</v>
+        <v>8.92</v>
       </c>
       <c r="M9" t="n">
         <v>1.46</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.58</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42494</v>
+        <v>42495</v>
       </c>
       <c r="H10" t="n">
-        <v>194</v>
+        <v>190.4</v>
       </c>
       <c r="I10" t="n">
         <v>190.7864515666213</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>4.11</v>
+        <v>2.17</v>
       </c>
       <c r="L10" t="n">
         <v>1.13</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>10.89</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42496</v>
+        <v>42499</v>
       </c>
       <c r="H11" t="n">
-        <v>191.85</v>
+        <v>215</v>
       </c>
       <c r="I11" t="n">
         <v>211.1390909644258</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.76</v>
+        <v>-12.92</v>
       </c>
       <c r="L11" t="n">
-        <v>2.84</v>
+        <v>15.34</v>
       </c>
       <c r="M11" t="n">
-        <v>0.16</v>
+        <v>0.65</v>
       </c>
       <c r="N11" t="n">
-        <v>0.76</v>
+        <v>12.07</v>
       </c>
       <c r="O11" t="n">
         <v>-1.86</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>16.13</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42685</v>
+        <v>42689</v>
       </c>
       <c r="H12" t="n">
-        <v>341.45</v>
+        <v>322.5</v>
       </c>
       <c r="I12" t="n">
         <v>335.5577106488927</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="K12" t="n">
-        <v>58.81</v>
+        <v>50</v>
       </c>
       <c r="L12" t="n">
         <v>10.19</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>21.34</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42748</v>
+        <v>42751</v>
       </c>
       <c r="H13" t="n">
-        <v>297.3</v>
+        <v>302.7</v>
       </c>
       <c r="I13" t="n">
         <v>301.6313616476694</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K13" t="n">
-        <v>7.81</v>
+        <v>6.14</v>
       </c>
       <c r="L13" t="n">
         <v>5.8</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.98</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43052</v>
+        <v>43053</v>
       </c>
       <c r="H14" t="n">
-        <v>467.05</v>
+        <v>451.35</v>
       </c>
       <c r="I14" t="n">
         <v>459.2838561393801</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K14" t="n">
-        <v>54.29</v>
+        <v>49.11</v>
       </c>
       <c r="L14" t="n">
         <v>5.43</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>204</v>
+        <v>205</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>11</v>
+      </c>
+      <c r="U14" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>15.08</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43089</v>
+        <v>43090</v>
       </c>
       <c r="H15" t="n">
-        <v>444.75</v>
+        <v>472.2</v>
       </c>
       <c r="I15" t="n">
         <v>460.4897398417867</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K15" t="n">
-        <v>1.46</v>
+        <v>-4.62</v>
       </c>
       <c r="L15" t="n">
-        <v>4.8</v>
+        <v>5.68</v>
       </c>
       <c r="M15" t="n">
         <v>1.49</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>12.32</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43116</v>
+        <v>43117</v>
       </c>
       <c r="H16" t="n">
-        <v>438.6</v>
+        <v>432.25</v>
       </c>
       <c r="I16" t="n">
         <v>434.2468575617539</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K16" t="n">
-        <v>-7.12</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>7.71</v>
+        <v>10.13</v>
       </c>
       <c r="M16" t="n">
         <v>0.61</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>9.4</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43194</v>
+        <v>43195</v>
       </c>
       <c r="H17" t="n">
-        <v>415.3</v>
+        <v>432.75</v>
       </c>
       <c r="I17" t="n">
         <v>417.8280642048999</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K17" t="n">
-        <v>3.92</v>
+        <v>-0.12</v>
       </c>
       <c r="L17" t="n">
         <v>2.94</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>11.64</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43236</v>
+        <v>43237</v>
       </c>
       <c r="H18" t="n">
-        <v>419.5</v>
+        <v>414.1</v>
       </c>
       <c r="I18" t="n">
         <v>414.7421972887145</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.06</v>
+        <v>-4.31</v>
       </c>
       <c r="L18" t="n">
-        <v>5.34</v>
+        <v>10.43</v>
       </c>
       <c r="M18" t="n">
-        <v>0.77</v>
+        <v>2.74</v>
       </c>
       <c r="N18" t="n">
         <v>2.47</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43290</v>
+        <v>43291</v>
       </c>
       <c r="H19" t="n">
-        <v>408.5</v>
+        <v>418.65</v>
       </c>
       <c r="I19" t="n">
         <v>411.4928956328209</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K19" t="n">
-        <v>1.35</v>
+        <v>-1.1</v>
       </c>
       <c r="L19" t="n">
         <v>2.98</v>
       </c>
       <c r="M19" t="n">
-        <v>0.99</v>
+        <v>1.11</v>
       </c>
       <c r="N19" t="n">
         <v>3.18</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.48</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43370</v>
+        <v>43371</v>
       </c>
       <c r="H20" t="n">
-        <v>416</v>
+        <v>403.4</v>
       </c>
       <c r="I20" t="n">
         <v>412.1491158586444</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.63</v>
+        <v>-3.64</v>
       </c>
       <c r="L20" t="n">
         <v>9.94</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>18.64</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43410</v>
+        <v>43413</v>
       </c>
       <c r="H21" t="n">
-        <v>444.6</v>
+        <v>460.8</v>
       </c>
       <c r="I21" t="n">
         <v>449.9011517797326</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K21" t="n">
-        <v>-10.21</v>
+        <v>-14.23</v>
       </c>
       <c r="L21" t="n">
-        <v>13.66</v>
+        <v>16.39</v>
       </c>
       <c r="M21" t="n">
         <v>2.63</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>14.44</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43493</v>
+        <v>43494</v>
       </c>
       <c r="H22" t="n">
-        <v>509.05</v>
+        <v>495.45</v>
       </c>
       <c r="I22" t="n">
         <v>499.3482097476319</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K22" t="n">
-        <v>10.47</v>
+        <v>7.52</v>
       </c>
       <c r="L22" t="n">
         <v>15.52</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>12.68</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H23" t="n">
-        <v>530.7</v>
+        <v>569.55</v>
       </c>
       <c r="I23" t="n">
         <v>549.079193772158</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K23" t="n">
-        <v>-7.11</v>
+        <v>-14.96</v>
       </c>
       <c r="L23" t="n">
-        <v>9.539999999999999</v>
+        <v>16.83</v>
       </c>
       <c r="M23" t="n">
         <v>1.96</v>
       </c>
       <c r="N23" t="n">
-        <v>6.45</v>
+        <v>7.32</v>
       </c>
       <c r="O23" t="n">
         <v>-2.67</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>13.58</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43591</v>
+        <v>43592</v>
       </c>
       <c r="H24" t="n">
-        <v>593.3</v>
+        <v>566.4</v>
       </c>
       <c r="I24" t="n">
         <v>576.8723777016268</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K24" t="n">
-        <v>4.17</v>
+        <v>-0.55</v>
       </c>
       <c r="L24" t="n">
         <v>7.82</v>
@@ -1809,7 +2096,7 @@
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>4.37</v>
+        <v>4.53</v>
       </c>
       <c r="O24" t="n">
         <v>7.32</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>12.5</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H25" t="n">
-        <v>579.4</v>
+        <v>618.05</v>
       </c>
       <c r="I25" t="n">
         <v>612.5915884727408</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.3</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>5.78</v>
+        <v>10.13</v>
       </c>
       <c r="M25" t="n">
-        <v>1.42</v>
+        <v>4.25</v>
       </c>
       <c r="N25" t="n">
-        <v>4.2</v>
+        <v>6.67</v>
       </c>
       <c r="O25" t="n">
         <v>-4.53</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>11.55</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43669</v>
+        <v>43670</v>
       </c>
       <c r="H26" t="n">
-        <v>609.55</v>
+        <v>590.55</v>
       </c>
       <c r="I26" t="n">
         <v>593.528325883777</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.38</v>
+        <v>-4.45</v>
       </c>
       <c r="L26" t="n">
-        <v>4.34</v>
+        <v>5.39</v>
       </c>
       <c r="M26" t="n">
         <v>0.51</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>11.86</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43685</v>
+        <v>43686</v>
       </c>
       <c r="H27" t="n">
-        <v>635.35</v>
+        <v>648.25</v>
       </c>
       <c r="I27" t="n">
         <v>641.0500228169881</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.59</v>
+        <v>-9.77</v>
       </c>
       <c r="L27" t="n">
-        <v>8.279999999999999</v>
+        <v>11</v>
       </c>
       <c r="M27" t="n">
         <v>0.99</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>8.98</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43711</v>
+        <v>43712</v>
       </c>
       <c r="H28" t="n">
-        <v>606.5</v>
+        <v>588.9</v>
       </c>
       <c r="I28" t="n">
         <v>590.0523231531063</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K28" t="n">
-        <v>-6.44</v>
+        <v>-9.16</v>
       </c>
       <c r="L28" t="n">
-        <v>8.609999999999999</v>
+        <v>10.35</v>
       </c>
       <c r="M28" t="n">
         <v>1.59</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>11.39</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43728</v>
+        <v>43731</v>
       </c>
       <c r="H29" t="n">
-        <v>629.55</v>
+        <v>645.05</v>
       </c>
       <c r="I29" t="n">
         <v>635.8170269533566</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.9</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>7.31</v>
+        <v>10.89</v>
       </c>
       <c r="M29" t="n">
         <v>0.87</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>10.33</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43780</v>
+        <v>43782</v>
       </c>
       <c r="H30" t="n">
-        <v>669.3</v>
+        <v>650.1</v>
       </c>
       <c r="I30" t="n">
         <v>650.2752192978605</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K30" t="n">
-        <v>3.76</v>
+        <v>0.78</v>
       </c>
       <c r="L30" t="n">
         <v>2.09</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>10.1</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43811</v>
+        <v>43812</v>
       </c>
       <c r="H31" t="n">
-        <v>712.8</v>
+        <v>717</v>
       </c>
       <c r="I31" t="n">
         <v>715.7510017561257</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K31" t="n">
-        <v>-9.640000000000001</v>
+        <v>-10.29</v>
       </c>
       <c r="L31" t="n">
         <v>13.41</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.76</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43896</v>
+        <v>43899</v>
       </c>
       <c r="H32" t="n">
-        <v>869.65</v>
+        <v>830.3</v>
       </c>
       <c r="I32" t="n">
         <v>841.8997004059324</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K32" t="n">
-        <v>21.29</v>
+        <v>15.8</v>
       </c>
       <c r="L32" t="n">
         <v>1.26</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>14.75</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43930</v>
+        <v>43934</v>
       </c>
       <c r="H33" t="n">
-        <v>734.95</v>
+        <v>746</v>
       </c>
       <c r="I33" t="n">
         <v>738.7578706695754</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K33" t="n">
-        <v>11.48</v>
+        <v>10.15</v>
       </c>
       <c r="L33" t="n">
         <v>4.03</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>27.12</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44054</v>
+        <v>44055</v>
       </c>
       <c r="H34" t="n">
-        <v>1174.2</v>
+        <v>1146.95</v>
       </c>
       <c r="I34" t="n">
         <v>1167.87426614032</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K34" t="n">
-        <v>57.4</v>
+        <v>53.75</v>
       </c>
       <c r="L34" t="n">
         <v>11.74</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>15.08</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44104</v>
+        <v>44105</v>
       </c>
       <c r="H35" t="n">
-        <v>1132.1</v>
+        <v>1153.75</v>
       </c>
       <c r="I35" t="n">
         <v>1152.02992045582</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K35" t="n">
-        <v>1.29</v>
+        <v>-0.59</v>
       </c>
       <c r="L35" t="n">
         <v>12.73</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>12.4</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c r="H36" t="n">
-        <v>1203</v>
+        <v>1174.65</v>
       </c>
       <c r="I36" t="n">
         <v>1175.224912730132</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K36" t="n">
-        <v>4.27</v>
+        <v>1.81</v>
       </c>
       <c r="L36" t="n">
         <v>3.91</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>11.21</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44236</v>
+        <v>44237</v>
       </c>
       <c r="H37" t="n">
-        <v>1186.6</v>
+        <v>1267.9</v>
       </c>
       <c r="I37" t="n">
         <v>1233.16963998832</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.02</v>
+        <v>-7.94</v>
       </c>
       <c r="L37" t="n">
-        <v>4.54</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="M37" t="n">
         <v>1.44</v>
       </c>
       <c r="N37" t="n">
-        <v>4.57</v>
+        <v>6.85</v>
       </c>
       <c r="O37" t="n">
         <v>-2.36</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>13.07</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44279</v>
+        <v>44280</v>
       </c>
       <c r="H38" t="n">
-        <v>1219.25</v>
+        <v>1187.05</v>
       </c>
       <c r="I38" t="n">
         <v>1202.957075336391</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.84</v>
+        <v>-6.38</v>
       </c>
       <c r="L38" t="n">
-        <v>6.14</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="M38" t="n">
         <v>4.76</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>10.67</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44333</v>
+        <v>44334</v>
       </c>
       <c r="H39" t="n">
-        <v>1221.55</v>
+        <v>1268.3</v>
       </c>
       <c r="I39" t="n">
         <v>1261.133117520718</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.91</v>
+        <v>-6.84</v>
       </c>
       <c r="L39" t="n">
-        <v>6.57</v>
+        <v>7.58</v>
       </c>
       <c r="M39" t="n">
         <v>2.16</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.32</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44417</v>
+        <v>44418</v>
       </c>
       <c r="H40" t="n">
-        <v>1499.2</v>
+        <v>1475</v>
       </c>
       <c r="I40" t="n">
         <v>1489.378149305927</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K40" t="n">
-        <v>18.21</v>
+        <v>16.3</v>
       </c>
       <c r="L40" t="n">
         <v>3.02</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>9.91</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44504</v>
+        <v>44508</v>
       </c>
       <c r="H41" t="n">
-        <v>1530.1</v>
+        <v>1659.4</v>
       </c>
       <c r="I41" t="n">
         <v>1570.906251150767</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.74</v>
+        <v>-12.5</v>
       </c>
       <c r="L41" t="n">
-        <v>9.289999999999999</v>
+        <v>14.11</v>
       </c>
       <c r="M41" t="n">
         <v>3.28</v>
       </c>
       <c r="N41" t="n">
-        <v>5.76</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O41" t="n">
         <v>-1.61</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>13.64</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44523</v>
+        <v>44524</v>
       </c>
       <c r="H42" t="n">
-        <v>1528.3</v>
+        <v>1496</v>
       </c>
       <c r="I42" t="n">
         <v>1525.902250104022</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K42" t="n">
-        <v>-7.9</v>
+        <v>-9.85</v>
       </c>
       <c r="L42" t="n">
-        <v>8.4</v>
+        <v>10.51</v>
       </c>
       <c r="M42" t="n">
         <v>0.55</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>11.58</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44561</v>
+        <v>44564</v>
       </c>
       <c r="H43" t="n">
-        <v>1495.65</v>
+        <v>1540.4</v>
       </c>
       <c r="I43" t="n">
         <v>1540.103765196716</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K43" t="n">
-        <v>0.02</v>
+        <v>-2.97</v>
       </c>
       <c r="L43" t="n">
-        <v>2.48</v>
+        <v>3.43</v>
       </c>
       <c r="M43" t="n">
         <v>1.62</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>8.99</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H44" t="n">
-        <v>1473.5</v>
+        <v>1432.75</v>
       </c>
       <c r="I44" t="n">
         <v>1436.095082540647</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.34</v>
+        <v>-6.99</v>
       </c>
       <c r="L44" t="n">
-        <v>6.06</v>
+        <v>7.82</v>
       </c>
       <c r="M44" t="n">
         <v>0.28</v>
       </c>
       <c r="N44" t="n">
-        <v>2.21</v>
+        <v>2.77</v>
       </c>
       <c r="O44" t="n">
         <v>2.99</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44743</v>
+        <v>44746</v>
       </c>
       <c r="H45" t="n">
-        <v>1042.65</v>
+        <v>1062.65</v>
       </c>
       <c r="I45" t="n">
         <v>1056.899892333839</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K45" t="n">
-        <v>27.23</v>
+        <v>25.83</v>
       </c>
       <c r="L45" t="n">
         <v>4.81</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>7</v>
+      </c>
+      <c r="U45" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>9.539999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44785</v>
+        <v>44789</v>
       </c>
       <c r="H46" t="n">
-        <v>1187.4</v>
+        <v>1040.1</v>
       </c>
       <c r="I46" t="n">
         <v>1080.849834456367</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K46" t="n">
-        <v>11.74</v>
+        <v>-2.12</v>
       </c>
       <c r="L46" t="n">
         <v>7.12</v>
       </c>
       <c r="M46" t="n">
-        <v>0.7</v>
+        <v>7.95</v>
       </c>
       <c r="N46" t="n">
-        <v>2.41</v>
+        <v>12.41</v>
       </c>
       <c r="O46" t="n">
         <v>1.92</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>15.53</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44840</v>
+        <v>44841</v>
       </c>
       <c r="H47" t="n">
-        <v>1043.95</v>
+        <v>1058.4</v>
       </c>
       <c r="I47" t="n">
         <v>1055.685579090074</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.37</v>
+        <v>-1.76</v>
       </c>
       <c r="L47" t="n">
         <v>5.09</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>9.93</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H48" t="n">
-        <v>1085.65</v>
+        <v>1043.45</v>
       </c>
       <c r="I48" t="n">
         <v>1066.313672939168</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K48" t="n">
-        <v>2.57</v>
+        <v>-1.41</v>
       </c>
       <c r="L48" t="n">
         <v>4.81</v>
@@ -3177,7 +3752,7 @@
         <v>1.95</v>
       </c>
       <c r="N48" t="n">
-        <v>3.53</v>
+        <v>3.89</v>
       </c>
       <c r="O48" t="n">
         <v>1.38</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>9.5</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45007</v>
+        <v>45008</v>
       </c>
       <c r="H49" t="n">
-        <v>971.65</v>
+        <v>981.85</v>
       </c>
       <c r="I49" t="n">
         <v>980.9487169599175</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K49" t="n">
-        <v>6.88</v>
+        <v>5.9</v>
       </c>
       <c r="L49" t="n">
         <v>5.67</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>7.13</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45149</v>
+        <v>45152</v>
       </c>
       <c r="H50" t="n">
-        <v>1350.05</v>
+        <v>1282.2</v>
       </c>
       <c r="I50" t="n">
         <v>1291.574462434346</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K50" t="n">
-        <v>37.5</v>
+        <v>30.59</v>
       </c>
       <c r="L50" t="n">
         <v>3.34</v>
       </c>
       <c r="M50" t="n">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="N50" t="n">
-        <v>2.18</v>
+        <v>5.03</v>
       </c>
       <c r="O50" t="n">
         <v>1.05</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>6</v>
+      </c>
+      <c r="U50" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7.56</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45225</v>
+        <v>45226</v>
       </c>
       <c r="H51" t="n">
-        <v>1262.9</v>
+        <v>1290.65</v>
       </c>
       <c r="I51" t="n">
         <v>1282.811153391633</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K51" t="n">
-        <v>1.51</v>
+        <v>-0.66</v>
       </c>
       <c r="L51" t="n">
         <v>4.43</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.52</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45308</v>
+        <v>45309</v>
       </c>
       <c r="H52" t="n">
-        <v>1417</v>
+        <v>1380.3</v>
       </c>
       <c r="I52" t="n">
         <v>1401.683540275962</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K52" t="n">
-        <v>9.789999999999999</v>
+        <v>6.95</v>
       </c>
       <c r="L52" t="n">
         <v>5.78</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45358</v>
+        <v>45362</v>
       </c>
       <c r="H53" t="n">
-        <v>1377.15</v>
+        <v>1401.65</v>
       </c>
       <c r="I53" t="n">
         <v>1401.325763112007</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K53" t="n">
-        <v>0.23</v>
+        <v>-1.55</v>
       </c>
       <c r="L53" t="n">
         <v>10.63</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>11.3</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H54" t="n">
-        <v>1930.35</v>
+        <v>1882</v>
       </c>
       <c r="I54" t="n">
         <v>1899.57478400852</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K54" t="n">
-        <v>37.72</v>
+        <v>34.27</v>
       </c>
       <c r="L54" t="n">
         <v>5.75</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>8</v>
+      </c>
+      <c r="U54" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>10.24</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45621</v>
+        <v>45622</v>
       </c>
       <c r="H55" t="n">
-        <v>1932.3</v>
+        <v>1951.8</v>
       </c>
       <c r="I55" t="n">
         <v>1934.415991446937</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.67</v>
+        <v>-3.71</v>
       </c>
       <c r="L55" t="n">
         <v>6.43</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45755</v>
+        <v>45756</v>
       </c>
       <c r="H56" t="n">
-        <v>2292.65</v>
+        <v>2139.95</v>
       </c>
       <c r="I56" t="n">
         <v>2202.20468324476</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K56" t="n">
-        <v>17.46</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L56" t="n">
         <v>2.91</v>
@@ -3633,7 +4304,7 @@
         <v>8.44</v>
       </c>
       <c r="N56" t="n">
-        <v>4</v>
+        <v>6.66</v>
       </c>
       <c r="O56" t="n">
         <v>1.01</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>6</v>
+      </c>
+      <c r="U56" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>14.64</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45811</v>
+        <v>45812</v>
       </c>
       <c r="H57" t="n">
-        <v>2234.4</v>
+        <v>2272.3</v>
       </c>
       <c r="I57" t="n">
         <v>2260.289801421432</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.41</v>
+        <v>-6.18</v>
       </c>
       <c r="L57" t="n">
         <v>9.380000000000001</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45881</v>
+        <v>45882</v>
       </c>
       <c r="H58" t="n">
-        <v>2533.2</v>
+        <v>2509.9</v>
       </c>
       <c r="I58" t="n">
         <v>2531.839770252921</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K58" t="n">
-        <v>11.48</v>
+        <v>10.46</v>
       </c>
       <c r="L58" t="n">
         <v>2.18</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>7.76</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45882</v>
+        <v>45883</v>
       </c>
       <c r="H59" t="n">
-        <v>2509.9</v>
+        <v>2757.4</v>
       </c>
       <c r="I59" t="n">
         <v>2704.652928088618</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>1.59</v>
+        <v>11.56</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>8.77</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="O59" t="n">
         <v>-0.92</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>10.19</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="H60" t="n">
-        <v>3829.6</v>
+        <v>3493.1</v>
       </c>
       <c r="I60" t="n">
         <v>3746.383598612966</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K60" t="n">
-        <v>38.88</v>
+        <v>26.68</v>
       </c>
       <c r="L60" t="n">
         <v>5.56</v>
       </c>
       <c r="M60" t="n">
-        <v>2.24</v>
+        <v>3.38</v>
       </c>
       <c r="N60" t="n">
-        <v>6.41</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="O60" t="n">
         <v>9.859999999999999</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>7</v>
+      </c>
+      <c r="U60" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>15.6</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="H61" t="n">
-        <v>3933.2</v>
+        <v>4066.9</v>
       </c>
       <c r="I61" t="n">
         <v>3951.769906611148</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K61" t="n">
-        <v>-12.6</v>
+        <v>-16.43</v>
       </c>
       <c r="L61" t="n">
-        <v>13.01</v>
+        <v>16.88</v>
       </c>
       <c r="M61" t="n">
         <v>5.37</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>13.64</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46066</v>
+        <v>46069</v>
       </c>
       <c r="H62" t="n">
-        <v>3586.1</v>
+        <v>3498.2</v>
       </c>
       <c r="I62" t="n">
         <v>3512.231336595639</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K62" t="n">
-        <v>-11.82</v>
+        <v>-13.98</v>
       </c>
       <c r="L62" t="n">
-        <v>12.64</v>
+        <v>15.17</v>
       </c>
       <c r="M62" t="n">
         <v>4.84</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>16.51</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H63" t="n">
-        <v>3475.2</v>
+        <v>3573.9</v>
       </c>
       <c r="I63" t="n">
         <v>3504.808437688039</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K63" t="n">
-        <v>0.66</v>
+        <v>-2.16</v>
       </c>
       <c r="L63" t="n">
         <v>2.34</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>12.22</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="H64" t="n">
-        <v>3342.9</v>
+        <v>3246.4</v>
       </c>
       <c r="I64" t="n">
         <v>3272.687769487803</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K64" t="n">
-        <v>-6.46</v>
+        <v>-9.16</v>
       </c>
       <c r="L64" t="n">
-        <v>9.449999999999999</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="M64" t="n">
         <v>2.1</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>10.14</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="H65" t="n">
-        <v>3166.9</v>
+        <v>3190.6</v>
       </c>
       <c r="I65" t="n">
         <v>3182.621507782782</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K65" t="n">
-        <v>2.45</v>
+        <v>1.72</v>
       </c>
       <c r="L65" t="n">
         <v>2.7</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>10.55</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="H66" t="n">
-        <v>2890.9</v>
+        <v>2870</v>
       </c>
       <c r="I66" t="n">
         <v>2881.17300766917</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K66" t="n">
-        <v>-9.390000000000001</v>
+        <v>-10.05</v>
       </c>
       <c r="L66" t="n">
         <v>16.29</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>12.27</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="H67" t="n">
-        <v>3022</v>
+        <v>3209</v>
       </c>
       <c r="I67" t="n">
         <v>3089.88819376145</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K67" t="n">
-        <v>-5.3</v>
+        <v>-11.81</v>
       </c>
       <c r="L67" t="n">
-        <v>6.45</v>
+        <v>11.81</v>
       </c>
       <c r="M67" t="n">
         <v>1.78</v>
       </c>
       <c r="N67" t="n">
-        <v>3.88</v>
+        <v>6.19</v>
       </c>
       <c r="O67" t="n">
         <v>-0.72</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>11.08</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="H68" t="n">
-        <v>2978.1</v>
+        <v>2905</v>
       </c>
       <c r="I68" t="n">
         <v>2954.493837465802</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K68" t="n">
-        <v>-7.2</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>7.2</v>
+        <v>9.94</v>
       </c>
       <c r="M68" t="n">
         <v>1.38</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,14 @@
       <c r="Q69" t="n">
         <v>39</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9335,7 +10170,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.6</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="6">
@@ -9345,7 +10180,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -9355,7 +10190,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8">
@@ -9365,7 +10200,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -9375,7 +10210,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79.5</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="10">
@@ -9385,7 +10220,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>125.2</v>
+        <v>126.2</v>
       </c>
     </row>
     <row r="11">
@@ -9425,7 +10260,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.61</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="15">
@@ -9435,7 +10270,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.49</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="16">
@@ -9445,7 +10280,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.41</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="17">
@@ -9455,7 +10290,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>58.81</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="18">
@@ -9465,7 +10300,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50.7</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="19">
@@ -9475,7 +10310,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.69</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -9485,7 +10320,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.8</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="21">
@@ -9495,7 +10330,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.29</v>
+        <v>16.88</v>
       </c>
     </row>
     <row r="22">
@@ -9505,7 +10340,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -9515,7 +10350,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
@@ -9525,7 +10360,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="25">
@@ -9545,7 +10380,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.06</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="27">
@@ -9565,7 +10400,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29">
